--- a/output/pdf_financials_xlsx/NSG.xlsx
+++ b/output/pdf_financials_xlsx/NSG.xlsx
@@ -1930,13 +1930,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>2.008834</v>
+        <v>2.861782</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>2.033682</v>
+        <v>2.881674</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>1.756772</v>
+        <v>2.653715</v>
       </c>
     </row>
     <row r="93">
@@ -3028,7 +3028,11 @@
           <t>Warrant reserves (note 9(c))</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" s="5" t="n">
         <v>0.852948</v>
       </c>

--- a/output/pdf_financials_xlsx/NSG.xlsx
+++ b/output/pdf_financials_xlsx/NSG.xlsx
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.263838</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.109842</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.043394</v>
       </c>
     </row>
     <row r="35">
@@ -1010,13 +1010,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.263838</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.109842</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.043394</v>
       </c>
     </row>
     <row r="37">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.438861</v>
+        <v>0.175023</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.183311</v>
+        <v>0.07346900000000001</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.066967</v>
+        <v>0.023573</v>
       </c>
     </row>
     <row r="49">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
